--- a/data/trans_orig/P42B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P42B-Habitat-trans_orig.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69070</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>89440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69070</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>89440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137711</t>
+          <t>138921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160971</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137711</t>
+          <t>138921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160971</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97313</t>
+          <t>96630</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>114627</t>
+          <t>114536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>97313</t>
+          <t>96630</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114627</t>
+          <t>114536</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>131954</t>
+          <t>131262</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>159162</t>
+          <t>159021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>131954</t>
+          <t>131262</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159162</t>
+          <t>159021</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>461134</t>
+          <t>464762</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>505826</t>
+          <t>508328</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>461134</t>
+          <t>464762</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>505826</t>
+          <t>508328</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3185,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3750,12 +3750,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>333912</t>
+          <t>332277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>376345</t>
+          <t>376301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>333912</t>
+          <t>332277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>376345</t>
+          <t>376301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88435</t>
+          <t>87769</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124677</t>
+          <t>124395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88435</t>
+          <t>87769</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124677</t>
+          <t>124395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>528779</t>
+          <t>533032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>581554</t>
+          <t>582820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528779</t>
+          <t>533032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581554</t>
+          <t>582820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>37143</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66304</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>37143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66304</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125279</t>
+          <t>122975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170886</t>
+          <t>168285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125279</t>
+          <t>122975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170886</t>
+          <t>168285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4772,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4865,12 +4865,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4928,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>464672</t>
+          <t>462722</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>509478</t>
+          <t>508319</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>464672</t>
+          <t>462722</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>509478</t>
+          <t>508319</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>80339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118495</t>
+          <t>118026</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>80339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118495</t>
+          <t>118026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -5244,12 +5244,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9778</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9778</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>549141</t>
+          <t>547204</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>600195</t>
+          <t>598960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>549141</t>
+          <t>547204</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>600195</t>
+          <t>598960</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39437</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>69309</t>
+          <t>68338</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39437</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69309</t>
+          <t>68338</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5606,12 +5606,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119932</t>
+          <t>121942</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>165209</t>
+          <t>166175</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119932</t>
+          <t>121942</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>165209</t>
+          <t>166175</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>58644</t>
+          <t>59349</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58644</t>
+          <t>59349</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5950,12 +5950,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>58598</t>
+          <t>58777</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>58598</t>
+          <t>58777</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1922137</t>
+          <t>1924753</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2021078</t>
+          <t>2026228</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1922137</t>
+          <t>1924753</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2021078</t>
+          <t>2026228</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -6106,12 +6106,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>137024</t>
+          <t>139302</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>191991</t>
+          <t>187221</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>137024</t>
+          <t>139302</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>191991</t>
+          <t>187221</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -6184,12 +6184,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>453392</t>
+          <t>450648</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>533758</t>
+          <t>532450</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -6219,12 +6219,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>453392</t>
+          <t>450648</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>533758</t>
+          <t>532450</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6515,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -6593,12 +6593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31971</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31971</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311845</t>
+          <t>312604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353176</t>
+          <t>351768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311845</t>
+          <t>312604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>353176</t>
+          <t>351768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -6827,12 +6827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40383</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40383</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>82998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117367</t>
+          <t>117481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>82998</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117367</t>
+          <t>117481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -7065,12 +7065,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7221,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>46086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7236,12 +7236,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7256,12 +7256,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>46086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -7299,12 +7299,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>580793</t>
+          <t>576857</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631228</t>
+          <t>631741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>580793</t>
+          <t>576857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631228</t>
+          <t>631741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67488</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67488</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104041</t>
+          <t>104941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146215</t>
+          <t>147118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104041</t>
+          <t>104941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146215</t>
+          <t>147118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7615,12 +7615,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7771,12 +7771,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>497268</t>
+          <t>495463</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>533084</t>
+          <t>531270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>497268</t>
+          <t>495463</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>533084</t>
+          <t>531270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -7927,12 +7927,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46335</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46335</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -8005,12 +8005,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24177</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24177</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>601962</t>
+          <t>601863</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>652655</t>
+          <t>651674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>601962</t>
+          <t>601863</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>652655</t>
+          <t>651674</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100841</t>
+          <t>102689</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143043</t>
+          <t>143162</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100841</t>
+          <t>102689</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>143043</t>
+          <t>143162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -8715,12 +8715,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>55623</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88261</t>
+          <t>88168</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>55623</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>88261</t>
+          <t>88168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -8871,12 +8871,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>73018</t>
+          <t>70914</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113067</t>
+          <t>110124</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>73018</t>
+          <t>70914</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>113067</t>
+          <t>110124</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -8949,12 +8949,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2030786</t>
+          <t>2030457</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2125029</t>
+          <t>2124350</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2030786</t>
+          <t>2030457</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2125029</t>
+          <t>2124350</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>124206</t>
+          <t>126334</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169769</t>
+          <t>170909</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9042,12 +9042,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>124206</t>
+          <t>126334</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>169769</t>
+          <t>170909</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -9105,12 +9105,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>342514</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>418034</t>
+          <t>420589</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>342514</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>418034</t>
+          <t>420589</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>808</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>808</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9622,22 +9622,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>250879</t>
+          <t>266504</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236265</t>
+          <t>250954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>265454</t>
+          <t>282083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>250879</t>
+          <t>266504</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>236265</t>
+          <t>250954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265454</t>
+          <t>282083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>72,77%</t>
         </is>
       </c>
     </row>
@@ -9743,22 +9743,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9778,22 +9778,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -9821,32 +9821,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65352</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54015</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78614</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9856,32 +9856,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65352</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54015</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78614</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -9899,17 +9899,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9934,17 +9934,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>387621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9981,32 +9981,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56328</t>
+          <t>57119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10016,32 +10016,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56328</t>
+          <t>57119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10137,32 +10137,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10172,32 +10172,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -10215,32 +10215,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>363957</t>
+          <t>406548</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343265</t>
+          <t>383486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>381887</t>
+          <t>426264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10250,32 +10250,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>363957</t>
+          <t>406548</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343265</t>
+          <t>383486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381887</t>
+          <t>426264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -10293,32 +10293,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10328,32 +10328,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -10371,32 +10371,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>84569</t>
+          <t>95021</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102382</t>
+          <t>113172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10406,32 +10406,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>84569</t>
+          <t>95021</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102382</t>
+          <t>113172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -10449,17 +10449,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>544262</t>
+          <t>604524</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544262</t>
+          <t>604524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544262</t>
+          <t>604524</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10484,17 +10484,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>544262</t>
+          <t>604524</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>544262</t>
+          <t>604524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544262</t>
+          <t>604524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41769</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54252</t>
+          <t>62061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10566,32 +10566,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41769</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54252</t>
+          <t>62061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -10609,32 +10609,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10644,32 +10644,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -10687,32 +10687,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10722,32 +10722,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -10765,32 +10765,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>279951</t>
+          <t>327854</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>219684</t>
+          <t>311013</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>309114</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10800,32 +10800,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>279951</t>
+          <t>327854</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>219684</t>
+          <t>311013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309114</t>
+          <t>344451</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -10843,32 +10843,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10878,32 +10878,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10921,32 +10921,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>87469</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54549</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165734</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10956,32 +10956,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>87469</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54549</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165734</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -10999,17 +10999,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>427129</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>427129</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>427129</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11034,17 +11034,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>427129</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>427129</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>427129</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11081,32 +11081,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42162</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11116,32 +11116,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42162</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -11237,32 +11237,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11272,32 +11272,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -11315,32 +11315,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>523153</t>
+          <t>490196</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>496505</t>
+          <t>470072</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>566773</t>
+          <t>506541</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11350,32 +11350,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>523153</t>
+          <t>490196</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>496505</t>
+          <t>470072</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>566773</t>
+          <t>506541</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -11393,32 +11393,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11428,32 +11428,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -11471,32 +11471,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>93082</t>
+          <t>103277</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63252</t>
+          <t>86788</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112207</t>
+          <t>121254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>93082</t>
+          <t>103277</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>63252</t>
+          <t>86788</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112207</t>
+          <t>121254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>669517</t>
+          <t>646650</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>669517</t>
+          <t>646650</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>669517</t>
+          <t>646650</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>669517</t>
+          <t>646650</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>669517</t>
+          <t>646650</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>669517</t>
+          <t>646650</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11631,32 +11631,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>119680</t>
+          <t>126478</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>99068</t>
+          <t>109037</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>142828</t>
+          <t>148213</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>119680</t>
+          <t>126478</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>99068</t>
+          <t>109037</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>142828</t>
+          <t>148213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -11709,32 +11709,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11744,32 +11744,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -11787,32 +11787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>78330</t>
+          <t>85819</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11822,32 +11822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>78330</t>
+          <t>85819</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -11865,32 +11865,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1417941</t>
+          <t>1491100</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1342767</t>
+          <t>1453666</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1477178</t>
+          <t>1527937</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -11900,32 +11900,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1417941</t>
+          <t>1491100</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1342767</t>
+          <t>1453666</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1477178</t>
+          <t>1527937</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -11943,32 +11943,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>73352</t>
+          <t>78491</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -11978,32 +11978,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>73352</t>
+          <t>78491</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -12021,32 +12021,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>330472</t>
+          <t>332538</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>286853</t>
+          <t>305272</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>430701</t>
+          <t>364157</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12056,32 +12056,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>330472</t>
+          <t>332538</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>286853</t>
+          <t>305272</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>430701</t>
+          <t>364157</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -12099,17 +12099,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2002631</t>
+          <t>2098487</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2002631</t>
+          <t>2098487</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2002631</t>
+          <t>2098487</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12134,17 +12134,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2002631</t>
+          <t>2098487</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2002631</t>
+          <t>2098487</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2002631</t>
+          <t>2098487</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
